--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-18T12:02:45+00:00</t>
+    <t>2023-04-24T21:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T20:59:20+00:00</t>
+    <t>2023-04-30T21:23:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T21:23:00+00:00</t>
+    <t>2023-05-05T00:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:13:03+00:00</t>
+    <t>2023-11-30T13:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T13:40:49+00:00</t>
+    <t>2023-11-30T14:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1637,7 +1637,7 @@
     <t>SCTCode</t>
   </si>
   <si>
-    <t>http://hl7.dk/fhir/core/ValueSet/TechniqesSCTCodes</t>
+    <t>http://hl7.dk/fhir/core/ValueSet/dk-core-TechniquesSCTCodes</t>
   </si>
   <si>
     <t>Observation.method.coding:SCTCode.id</t>
@@ -2589,7 +2589,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.4921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="57.31640625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T14:55:40+00:00</t>
+    <t>2023-12-01T12:31:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T12:31:40+00:00</t>
+    <t>2023-12-01T13:42:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T13:42:49+00:00</t>
+    <t>2023-12-19T10:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -13664,7 +13664,7 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:28:26+00:00</t>
+    <t>2023-12-19T10:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:34:37+00:00</t>
+    <t>2024-01-06T18:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T18:57:36+00:00</t>
+    <t>2024-01-08T22:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:06+00:00</t>
+    <t>2024-01-08T22:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:40+00:00</t>
+    <t>2024-03-19T10:43:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T10:43:29+00:00</t>
+    <t>2024-04-03T07:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1244,7 +1244,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -2574,7 +2574,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="218.36328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:46:18+00:00</t>
+    <t>2024-04-03T10:16:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1244,7 +1244,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|RelatedPerson)
 </t>
   </si>
   <si>
@@ -2574,7 +2574,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="218.36328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T10:16:02+00:00</t>
+    <t>2024-04-10T06:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -1244,7 +1244,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -2574,7 +2574,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="218.36328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T13:03:24+00:00</t>
+    <t>2024-05-06T06:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T07:49:19+00:00</t>
+    <t>2024-05-06T14:14:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T14:14:33+00:00</t>
+    <t>2024-05-10T08:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7056" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7056" uniqueCount="728">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1656,6 +1656,9 @@
   </si>
   <si>
     <t>Observation.method.coding.system</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct|http://snomed.info/sct/554471000005108</t>
   </si>
   <si>
     <t>Observation.method.coding:SCTCode.version</t>
@@ -14007,7 +14010,7 @@
         <v>82</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>294</v>
+        <v>532</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>82</v>
@@ -14081,10 +14084,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14201,10 +14204,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14321,10 +14324,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14441,10 +14444,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14563,10 +14566,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14685,10 +14688,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14711,16 +14714,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14770,7 +14773,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14788,27 +14791,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14831,16 +14834,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14890,7 +14893,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14908,27 +14911,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14951,19 +14954,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15012,7 +15015,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15024,7 +15027,7 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -15033,10 +15036,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15047,10 +15050,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15165,10 +15168,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15285,14 +15288,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15314,10 +15317,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>142</v>
@@ -15372,7 +15375,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15407,10 +15410,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15433,13 +15436,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15490,7 +15493,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15499,7 +15502,7 @@
         <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>105</v>
@@ -15511,10 +15514,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15525,10 +15528,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15551,13 +15554,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15608,7 +15611,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15617,7 +15620,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>105</v>
@@ -15629,10 +15632,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15643,10 +15646,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15672,16 +15675,16 @@
         <v>191</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15709,10 +15712,10 @@
         <v>117</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15730,7 +15733,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15748,10 +15751,10 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>491</v>
@@ -15765,10 +15768,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15794,16 +15797,16 @@
         <v>191</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15831,10 +15834,10 @@
         <v>206</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15852,7 +15855,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15870,10 +15873,10 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>491</v>
@@ -15887,10 +15890,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15913,17 +15916,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15972,7 +15975,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15996,7 +15999,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -16007,10 +16010,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16036,10 +16039,10 @@
         <v>216</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16090,7 +16093,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16111,10 +16114,10 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16125,10 +16128,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16151,16 +16154,16 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16210,7 +16213,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16231,10 +16234,10 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16245,10 +16248,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16271,16 +16274,16 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16330,7 +16333,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16351,10 +16354,10 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16365,10 +16368,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16391,19 +16394,19 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16452,7 +16455,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16473,10 +16476,10 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16487,10 +16490,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16605,10 +16608,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16725,14 +16728,14 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16754,10 +16757,10 @@
         <v>139</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>142</v>
@@ -16812,7 +16815,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16847,10 +16850,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16876,13 +16879,13 @@
         <v>191</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O119" t="s" s="2">
         <v>205</v>
@@ -16934,7 +16937,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>93</v>
@@ -16952,7 +16955,7 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>211</v>
@@ -16969,10 +16972,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17087,10 +17090,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17207,10 +17210,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17327,10 +17330,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>238</v>
@@ -17451,10 +17454,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17569,10 +17572,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17689,10 +17692,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17811,10 +17814,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17931,10 +17934,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18051,10 +18054,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18171,10 +18174,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18293,10 +18296,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>289</v>
@@ -18417,10 +18420,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18535,10 +18538,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18655,10 +18658,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18777,10 +18780,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18897,10 +18900,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19017,10 +19020,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19137,10 +19140,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19259,10 +19262,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>300</v>
@@ -19383,10 +19386,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19501,10 +19504,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19621,10 +19624,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19743,10 +19746,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19863,10 +19866,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19983,10 +19986,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20103,10 +20106,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20225,10 +20228,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>311</v>
@@ -20349,10 +20352,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20467,10 +20470,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20587,10 +20590,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20709,10 +20712,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20829,10 +20832,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20949,10 +20952,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21069,10 +21072,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21191,10 +21194,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>322</v>
@@ -21315,10 +21318,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21433,10 +21436,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21553,10 +21556,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21675,10 +21678,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21795,10 +21798,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21915,10 +21918,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22035,10 +22038,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22157,10 +22160,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>333</v>
@@ -22188,7 +22191,7 @@
         <v>228</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M163" t="s" s="2">
         <v>230</v>
@@ -22281,10 +22284,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22399,10 +22402,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22519,10 +22522,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22641,10 +22644,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22761,10 +22764,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22881,10 +22884,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23001,10 +23004,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23123,10 +23126,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23245,10 +23248,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23274,13 +23277,13 @@
         <v>407</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>409</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O172" t="s" s="2">
         <v>411</v>
@@ -23330,7 +23333,7 @@
         <v>225</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23348,7 +23351,7 @@
         <v>82</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>415</v>
@@ -23365,10 +23368,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>419</v>
@@ -23396,13 +23399,13 @@
         <v>420</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>409</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>411</v>
@@ -23454,7 +23457,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23472,7 +23475,7 @@
         <v>82</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>415</v>
@@ -23489,10 +23492,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23607,10 +23610,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23727,10 +23730,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23849,10 +23852,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23971,10 +23974,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24091,10 +24094,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24211,10 +24214,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24333,10 +24336,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24362,13 +24365,13 @@
         <v>191</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O181" t="s" s="2">
         <v>475</v>
@@ -24420,7 +24423,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24455,10 +24458,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24542,7 +24545,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24577,10 +24580,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24606,16 +24609,16 @@
         <v>83</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24664,7 +24667,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24685,10 +24688,10 @@
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1099,7 +1099,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|Location|Device)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|http://hl7.dk/fhir/core/StructureDefinition/dk-core-location|Device)
 </t>
   </si>
   <si>
@@ -1244,7 +1244,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$183</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:41:58+00:00</t>
+    <t>2024-05-12T09:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
+    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-observation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -279,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}dk-core-observation-mandatory-units:If value is specified then unit and/or code must be specified {value.ofType(Quantity).value.exists() implies value.ofType(Quantity).unit.exists() or value.ofType(Quantity).code.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}ipa-obs-1:If there is no component or hasMember element then either a value[x] or a data absent reason must be present {(component.empty() and hasMember.empty()) implies (dataAbsentReason or value)}dk-core-observation-mandatory-units:If value is specified then unit and/or code must be specified {value.ofType(Quantity).value.exists() implies value.ofType(Quantity).unit.exists() or value.ofType(Quantity).code.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1099,7 +1102,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|http://hl7.dk/fhir/core/StructureDefinition/dk-core-location|Device)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient)
 </t>
   </si>
   <si>
@@ -1244,7 +1247,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|Organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1292,8 +1295,8 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">obs-7
-</t>
+    <t>obs-7
+ipa-obs-1</t>
   </si>
   <si>
     <t>&lt; 441742003 |Evaluation finding|</t>
@@ -1495,8 +1498,8 @@
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
-    <t xml:space="preserve">obs-6
-</t>
+    <t>obs-6
+ipa-obs-1</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -1656,9 +1659,6 @@
   </si>
   <si>
     <t>Observation.method.coding.system</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct|http://snomed.info/sct/554471000005108</t>
   </si>
   <si>
     <t>Observation.method.coding:SCTCode.version</t>
@@ -1929,7 +1929,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -2251,6 +2251,10 @@
   <si>
     <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obs-6
+</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -2391,6 +2395,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2577,7 +2596,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="218.88671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2738,7 +2757,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2858,7 +2877,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>92</v>
       </c>
@@ -2978,7 +2997,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>100</v>
       </c>
@@ -3096,7 +3115,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>106</v>
       </c>
@@ -3216,7 +3235,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>112</v>
       </c>
@@ -3336,7 +3355,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>121</v>
       </c>
@@ -3456,7 +3475,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>129</v>
       </c>
@@ -3576,7 +3595,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>137</v>
       </c>
@@ -3696,7 +3715,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>145</v>
       </c>
@@ -3818,7 +3837,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>150</v>
       </c>
@@ -3938,7 +3957,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>159</v>
       </c>
@@ -4058,7 +4077,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>168</v>
       </c>
@@ -4178,7 +4197,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>177</v>
       </c>
@@ -4197,7 +4216,7 @@
         <v>93</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>94</v>
@@ -4300,7 +4319,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>190</v>
       </c>
@@ -4319,7 +4338,7 @@
         <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>82</v>
@@ -4422,7 +4441,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>200</v>
       </c>
@@ -4441,7 +4460,7 @@
         <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
@@ -4544,7 +4563,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>215</v>
       </c>
@@ -4662,7 +4681,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>221</v>
       </c>
@@ -4782,7 +4801,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>227</v>
       </c>
@@ -4902,7 +4921,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>237</v>
       </c>
@@ -5026,7 +5045,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>240</v>
       </c>
@@ -5144,7 +5163,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>242</v>
       </c>
@@ -5264,7 +5283,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>244</v>
       </c>
@@ -5386,7 +5405,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>254</v>
       </c>
@@ -5506,7 +5525,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>262</v>
       </c>
@@ -5626,7 +5645,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>270</v>
       </c>
@@ -5746,7 +5765,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>278</v>
       </c>
@@ -5868,7 +5887,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>288</v>
       </c>
@@ -5992,7 +6011,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>291</v>
       </c>
@@ -6110,7 +6129,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>292</v>
       </c>
@@ -6230,7 +6249,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>293</v>
       </c>
@@ -6352,7 +6371,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>295</v>
       </c>
@@ -6472,7 +6491,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>296</v>
       </c>
@@ -6592,7 +6611,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>297</v>
       </c>
@@ -6712,7 +6731,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>298</v>
       </c>
@@ -6834,7 +6853,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>299</v>
       </c>
@@ -6958,7 +6977,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>302</v>
       </c>
@@ -7076,7 +7095,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>303</v>
       </c>
@@ -7196,7 +7215,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>304</v>
       </c>
@@ -7318,7 +7337,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>306</v>
       </c>
@@ -7438,7 +7457,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>307</v>
       </c>
@@ -7558,7 +7577,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>308</v>
       </c>
@@ -7678,7 +7697,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>309</v>
       </c>
@@ -7800,7 +7819,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>310</v>
       </c>
@@ -7924,7 +7943,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>313</v>
       </c>
@@ -8042,7 +8061,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>314</v>
       </c>
@@ -8162,7 +8181,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>315</v>
       </c>
@@ -8284,7 +8303,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>317</v>
       </c>
@@ -8404,7 +8423,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>318</v>
       </c>
@@ -8524,7 +8543,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>319</v>
       </c>
@@ -8644,7 +8663,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>320</v>
       </c>
@@ -8766,7 +8785,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>321</v>
       </c>
@@ -8890,7 +8909,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>324</v>
       </c>
@@ -9008,7 +9027,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>325</v>
       </c>
@@ -9128,7 +9147,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>326</v>
       </c>
@@ -9250,7 +9269,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>328</v>
       </c>
@@ -9370,7 +9389,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>329</v>
       </c>
@@ -9490,7 +9509,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>330</v>
       </c>
@@ -9610,7 +9629,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>331</v>
       </c>
@@ -9732,7 +9751,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>332</v>
       </c>
@@ -9856,7 +9875,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>335</v>
       </c>
@@ -9974,7 +9993,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>336</v>
       </c>
@@ -10094,7 +10113,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>337</v>
       </c>
@@ -10216,7 +10235,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>339</v>
       </c>
@@ -10336,7 +10355,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>340</v>
       </c>
@@ -10456,7 +10475,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>341</v>
       </c>
@@ -10576,7 +10595,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>342</v>
       </c>
@@ -10698,7 +10717,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>343</v>
       </c>
@@ -10820,7 +10839,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>351</v>
       </c>
@@ -10839,7 +10858,7 @@
         <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>82</v>
@@ -10942,7 +10961,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>361</v>
       </c>
@@ -11062,7 +11081,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>367</v>
       </c>
@@ -11184,7 +11203,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>378</v>
       </c>
@@ -11203,7 +11222,7 @@
         <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>82</v>
@@ -11306,7 +11325,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>389</v>
       </c>
@@ -11426,7 +11445,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
         <v>397</v>
       </c>
@@ -11546,7 +11565,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>406</v>
       </c>
@@ -11565,7 +11584,7 @@
         <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>82</v>
@@ -11666,7 +11685,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
         <v>418</v>
       </c>
@@ -11687,7 +11706,7 @@
         <v>93</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -11790,7 +11809,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
         <v>421</v>
       </c>
@@ -11908,7 +11927,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
         <v>423</v>
       </c>
@@ -12028,7 +12047,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
         <v>425</v>
       </c>
@@ -12150,7 +12169,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
         <v>435</v>
       </c>
@@ -12272,7 +12291,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
         <v>446</v>
       </c>
@@ -12392,7 +12411,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
         <v>454</v>
       </c>
@@ -12512,7 +12531,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
         <v>463</v>
       </c>
@@ -12634,7 +12653,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
         <v>471</v>
       </c>
@@ -12653,7 +12672,7 @@
         <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
@@ -12756,7 +12775,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
         <v>481</v>
       </c>
@@ -12878,7 +12897,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
         <v>493</v>
       </c>
@@ -13000,7 +13019,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
         <v>501</v>
       </c>
@@ -13120,7 +13139,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
         <v>511</v>
       </c>
@@ -13242,7 +13261,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
         <v>520</v>
       </c>
@@ -13360,7 +13379,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
         <v>521</v>
       </c>
@@ -13480,7 +13499,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
         <v>522</v>
       </c>
@@ -13600,7 +13619,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
         <v>523</v>
       </c>
@@ -13722,7 +13741,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
         <v>526</v>
       </c>
@@ -13840,7 +13859,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
         <v>528</v>
       </c>
@@ -13960,7 +13979,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
         <v>530</v>
       </c>
@@ -14010,7 +14029,7 @@
         <v>82</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>532</v>
+        <v>294</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>82</v>
@@ -14082,12 +14101,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14202,12 +14221,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14322,12 +14341,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14442,12 +14461,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14564,12 +14583,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14686,12 +14705,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14714,16 +14733,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14773,7 +14792,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14791,27 +14810,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="AM101" t="s" s="2">
+      <c r="AN101" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="AN101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="AO101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP101" t="s" s="2">
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
         <v>550</v>
       </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s" s="2">
-        <v>551</v>
-      </c>
       <c r="B102" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14834,16 +14853,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14893,7 +14912,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14911,27 +14930,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AM102" t="s" s="2">
+      <c r="AN102" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="AN102" t="s" s="2">
+      <c r="AO102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP102" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="AO102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP102" t="s" s="2">
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
         <v>559</v>
       </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s" s="2">
-        <v>560</v>
-      </c>
       <c r="B103" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14954,19 +14973,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15015,7 +15034,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15027,33 +15046,33 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="AK103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM103" t="s" s="2">
+      <c r="AN103" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="AN103" t="s" s="2">
+      <c r="AO103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="AO103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s" s="2">
-        <v>569</v>
-      </c>
       <c r="B104" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15166,12 +15185,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15286,16 +15305,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15317,10 +15336,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>142</v>
@@ -15375,7 +15394,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15408,12 +15427,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15436,13 +15455,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15493,7 +15512,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15502,7 +15521,7 @@
         <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>105</v>
@@ -15514,24 +15533,24 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="AN107" t="s" s="2">
+      <c r="AO107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AO107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s" s="2">
-        <v>583</v>
-      </c>
       <c r="B108" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15554,13 +15573,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15611,7 +15630,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15620,7 +15639,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>105</v>
@@ -15632,24 +15651,24 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AN108" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AO108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s" s="2">
-        <v>587</v>
-      </c>
       <c r="B109" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15675,16 +15694,16 @@
         <v>191</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="N109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15712,11 +15731,11 @@
         <v>117</v>
       </c>
       <c r="Y109" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="Z109" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="Z109" t="s" s="2">
-        <v>593</v>
-      </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15733,7 +15752,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15751,10 +15770,10 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>491</v>
@@ -15766,12 +15785,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15797,16 +15816,16 @@
         <v>191</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15834,11 +15853,11 @@
         <v>206</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="Z110" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="Z110" t="s" s="2">
-        <v>602</v>
-      </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15855,7 +15874,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15873,10 +15892,10 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AM110" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>491</v>
@@ -15888,12 +15907,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15916,17 +15935,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15975,7 +15994,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15999,21 +16018,21 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="AO111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP111" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s" s="2">
-        <v>609</v>
-      </c>
       <c r="B112" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16039,10 +16058,10 @@
         <v>216</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16093,7 +16112,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16114,24 +16133,24 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AN112" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="AO112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s" s="2">
-        <v>613</v>
-      </c>
       <c r="B113" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16154,16 +16173,16 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16213,7 +16232,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16234,24 +16253,24 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AN113" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="AN113" t="s" s="2">
+      <c r="AO113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="AO113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP113" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s" s="2">
-        <v>620</v>
-      </c>
       <c r="B114" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16274,16 +16293,16 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16333,7 +16352,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16354,24 +16373,24 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AN114" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="AO114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s" s="2">
-        <v>626</v>
-      </c>
       <c r="B115" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16394,19 +16413,19 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16455,7 +16474,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16476,24 +16495,24 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="AN115" t="s" s="2">
+      <c r="AO115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP115" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="AO115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP115" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s" s="2">
-        <v>633</v>
-      </c>
       <c r="B116" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16606,12 +16625,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16726,16 +16745,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16757,10 +16776,10 @@
         <v>139</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>142</v>
@@ -16815,7 +16834,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16848,12 +16867,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16879,13 +16898,13 @@
         <v>191</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="O119" t="s" s="2">
         <v>205</v>
@@ -16937,7 +16956,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>93</v>
@@ -16955,7 +16974,7 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>211</v>
@@ -16970,12 +16989,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17088,12 +17107,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17208,12 +17227,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17328,12 +17347,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>238</v>
@@ -17452,12 +17471,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17570,12 +17589,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B125" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17690,12 +17709,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B126" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17812,12 +17831,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="B127" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17932,12 +17951,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>654</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18052,12 +18071,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B129" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18172,12 +18191,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="B130" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18294,12 +18313,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>289</v>
@@ -18418,12 +18437,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18536,12 +18555,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18656,12 +18675,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18778,12 +18797,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18898,12 +18917,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19018,12 +19037,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19138,12 +19157,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19260,12 +19279,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>300</v>
@@ -19384,12 +19403,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19502,12 +19521,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19622,12 +19641,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19744,12 +19763,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19864,12 +19883,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19984,12 +20003,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20104,12 +20123,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20226,12 +20245,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>311</v>
@@ -20350,12 +20369,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20468,12 +20487,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20588,12 +20607,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20710,12 +20729,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20830,12 +20849,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20950,12 +20969,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21070,12 +21089,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21192,12 +21211,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>322</v>
@@ -21316,12 +21335,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21434,12 +21453,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21554,12 +21573,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21676,12 +21695,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21796,12 +21815,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21916,12 +21935,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22036,12 +22055,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22158,12 +22177,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>333</v>
@@ -22191,7 +22210,7 @@
         <v>228</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="M163" t="s" s="2">
         <v>230</v>
@@ -22282,12 +22301,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22400,12 +22419,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22520,12 +22539,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22642,12 +22661,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22762,12 +22781,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22882,12 +22901,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23002,12 +23021,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23124,12 +23143,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23246,12 +23265,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23277,13 +23296,13 @@
         <v>407</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>409</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="O172" t="s" s="2">
         <v>411</v>
@@ -23333,7 +23352,7 @@
         <v>225</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23351,7 +23370,7 @@
         <v>82</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>415</v>
@@ -23366,12 +23385,12 @@
         <v>417</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>419</v>
@@ -23399,13 +23418,13 @@
         <v>420</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>409</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>411</v>
@@ -23457,7 +23476,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23475,7 +23494,7 @@
         <v>82</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>415</v>
@@ -23490,12 +23509,12 @@
         <v>417</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="B174" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23608,12 +23627,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="B175" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23728,12 +23747,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="B176" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23850,12 +23869,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="B177" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23972,12 +23991,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="B178" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24092,12 +24111,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="B179" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24212,12 +24231,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="B180" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24334,12 +24353,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24365,13 +24384,13 @@
         <v>191</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="M181" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="M181" t="s" s="2">
+      <c r="N181" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="O181" t="s" s="2">
         <v>475</v>
@@ -24423,7 +24442,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24432,7 +24451,7 @@
         <v>93</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>479</v>
+        <v>723</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>105</v>
@@ -24456,7 +24475,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
         <v>724</v>
       </c>
@@ -24578,7 +24597,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
         <v>725</v>
       </c>
@@ -24615,10 +24634,10 @@
         <v>727</v>
       </c>
       <c r="N183" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="O183" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24688,10 +24707,10 @@
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AN183" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AN183" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>
@@ -24701,6 +24720,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AP183">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI182">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$183</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7056" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7056" uniqueCount="727">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T11:37:02+00:00</t>
+    <t>2024-06-03T20:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-observation</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -282,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}ipa-obs-1:If there is no component or hasMember element then either a value[x] or a data absent reason must be present {(component.empty() and hasMember.empty()) implies (dataAbsentReason or value)}dk-core-observation-mandatory-units:If value is specified then unit and/or code must be specified {value.ofType(Quantity).value.exists() implies value.ofType(Quantity).unit.exists() or value.ofType(Quantity).code.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}dk-core-observation-mandatory-units:If value is specified then unit and/or code must be specified {value.ofType(Quantity).value.exists() implies value.ofType(Quantity).unit.exists() or value.ofType(Quantity).code.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1102,7 +1099,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|Location|Device)
 </t>
   </si>
   <si>
@@ -1295,8 +1292,8 @@
 </t>
   </si>
   <si>
-    <t>obs-7
-ipa-obs-1</t>
+    <t xml:space="preserve">obs-7
+</t>
   </si>
   <si>
     <t>&lt; 441742003 |Evaluation finding|</t>
@@ -1498,8 +1495,8 @@
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
-    <t>obs-6
-ipa-obs-1</t>
+    <t xml:space="preserve">obs-6
+</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -1929,7 +1926,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -2251,10 +2248,6 @@
   <si>
     <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-6
-</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -2395,21 +2388,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -2757,7 +2735,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2877,7 +2855,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>92</v>
       </c>
@@ -2997,7 +2975,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>100</v>
       </c>
@@ -3115,7 +3093,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>106</v>
       </c>
@@ -3235,7 +3213,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>112</v>
       </c>
@@ -3355,7 +3333,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>121</v>
       </c>
@@ -3475,7 +3453,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>129</v>
       </c>
@@ -3595,7 +3573,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>137</v>
       </c>
@@ -3715,7 +3693,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>145</v>
       </c>
@@ -3837,7 +3815,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>150</v>
       </c>
@@ -3957,7 +3935,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>159</v>
       </c>
@@ -4077,7 +4055,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>168</v>
       </c>
@@ -4197,7 +4175,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>177</v>
       </c>
@@ -4216,7 +4194,7 @@
         <v>93</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>94</v>
@@ -4319,7 +4297,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>190</v>
       </c>
@@ -4338,7 +4316,7 @@
         <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>82</v>
@@ -4441,7 +4419,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>200</v>
       </c>
@@ -4460,7 +4438,7 @@
         <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
@@ -4563,7 +4541,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>215</v>
       </c>
@@ -4681,7 +4659,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>221</v>
       </c>
@@ -4801,7 +4779,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>227</v>
       </c>
@@ -4921,7 +4899,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>237</v>
       </c>
@@ -5045,7 +5023,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>240</v>
       </c>
@@ -5163,7 +5141,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>242</v>
       </c>
@@ -5283,7 +5261,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>244</v>
       </c>
@@ -5405,7 +5383,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>254</v>
       </c>
@@ -5525,7 +5503,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>262</v>
       </c>
@@ -5645,7 +5623,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>270</v>
       </c>
@@ -5765,7 +5743,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>278</v>
       </c>
@@ -5887,7 +5865,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>288</v>
       </c>
@@ -6011,7 +5989,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>291</v>
       </c>
@@ -6129,7 +6107,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>292</v>
       </c>
@@ -6249,7 +6227,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>293</v>
       </c>
@@ -6371,7 +6349,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>295</v>
       </c>
@@ -6491,7 +6469,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>296</v>
       </c>
@@ -6611,7 +6589,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>297</v>
       </c>
@@ -6731,7 +6709,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>298</v>
       </c>
@@ -6853,7 +6831,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>299</v>
       </c>
@@ -6977,7 +6955,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>302</v>
       </c>
@@ -7095,7 +7073,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>303</v>
       </c>
@@ -7215,7 +7193,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>304</v>
       </c>
@@ -7337,7 +7315,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>306</v>
       </c>
@@ -7457,7 +7435,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>307</v>
       </c>
@@ -7577,7 +7555,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>308</v>
       </c>
@@ -7697,7 +7675,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>309</v>
       </c>
@@ -7819,7 +7797,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>310</v>
       </c>
@@ -7943,7 +7921,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>313</v>
       </c>
@@ -8061,7 +8039,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>314</v>
       </c>
@@ -8181,7 +8159,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>315</v>
       </c>
@@ -8303,7 +8281,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>317</v>
       </c>
@@ -8423,7 +8401,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>318</v>
       </c>
@@ -8543,7 +8521,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>319</v>
       </c>
@@ -8663,7 +8641,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>320</v>
       </c>
@@ -8785,7 +8763,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>321</v>
       </c>
@@ -8909,7 +8887,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>324</v>
       </c>
@@ -9027,7 +9005,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>325</v>
       </c>
@@ -9147,7 +9125,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>326</v>
       </c>
@@ -9269,7 +9247,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>328</v>
       </c>
@@ -9389,7 +9367,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>329</v>
       </c>
@@ -9509,7 +9487,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>330</v>
       </c>
@@ -9629,7 +9607,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>331</v>
       </c>
@@ -9751,7 +9729,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>332</v>
       </c>
@@ -9875,7 +9853,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>335</v>
       </c>
@@ -9993,7 +9971,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>336</v>
       </c>
@@ -10113,7 +10091,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>337</v>
       </c>
@@ -10235,7 +10213,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>339</v>
       </c>
@@ -10355,7 +10333,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>340</v>
       </c>
@@ -10475,7 +10453,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>341</v>
       </c>
@@ -10595,7 +10573,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>342</v>
       </c>
@@ -10717,7 +10695,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>343</v>
       </c>
@@ -10839,7 +10817,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>351</v>
       </c>
@@ -10858,7 +10836,7 @@
         <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>82</v>
@@ -10961,7 +10939,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>361</v>
       </c>
@@ -11081,7 +11059,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>367</v>
       </c>
@@ -11203,7 +11181,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>378</v>
       </c>
@@ -11222,7 +11200,7 @@
         <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>82</v>
@@ -11325,7 +11303,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>389</v>
       </c>
@@ -11445,7 +11423,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>397</v>
       </c>
@@ -11565,7 +11543,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
         <v>406</v>
       </c>
@@ -11584,7 +11562,7 @@
         <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>82</v>
@@ -11685,7 +11663,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
         <v>418</v>
       </c>
@@ -11706,7 +11684,7 @@
         <v>93</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -11809,7 +11787,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
         <v>421</v>
       </c>
@@ -11927,7 +11905,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>423</v>
       </c>
@@ -12047,7 +12025,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
         <v>425</v>
       </c>
@@ -12169,7 +12147,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>435</v>
       </c>
@@ -12291,7 +12269,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>446</v>
       </c>
@@ -12411,7 +12389,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>454</v>
       </c>
@@ -12531,7 +12509,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>463</v>
       </c>
@@ -12653,7 +12631,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>471</v>
       </c>
@@ -12672,7 +12650,7 @@
         <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
@@ -12775,7 +12753,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
         <v>481</v>
       </c>
@@ -12897,7 +12875,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
         <v>493</v>
       </c>
@@ -13019,7 +12997,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>501</v>
       </c>
@@ -13139,7 +13117,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
         <v>511</v>
       </c>
@@ -13261,7 +13239,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>520</v>
       </c>
@@ -13379,7 +13357,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
         <v>521</v>
       </c>
@@ -13499,7 +13477,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
         <v>522</v>
       </c>
@@ -13619,7 +13597,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
         <v>523</v>
       </c>
@@ -13741,7 +13719,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
         <v>526</v>
       </c>
@@ -13859,7 +13837,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>528</v>
       </c>
@@ -13979,7 +13957,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
         <v>530</v>
       </c>
@@ -14101,7 +14079,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>532</v>
       </c>
@@ -14221,7 +14199,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
         <v>534</v>
       </c>
@@ -14341,7 +14319,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
         <v>536</v>
       </c>
@@ -14461,7 +14439,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
         <v>538</v>
       </c>
@@ -14583,7 +14561,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
         <v>540</v>
       </c>
@@ -14705,7 +14683,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
         <v>541</v>
       </c>
@@ -14825,7 +14803,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
         <v>550</v>
       </c>
@@ -14945,7 +14923,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
         <v>559</v>
       </c>
@@ -15067,7 +15045,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>568</v>
       </c>
@@ -15185,7 +15163,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
         <v>569</v>
       </c>
@@ -15305,7 +15283,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
         <v>570</v>
       </c>
@@ -15427,7 +15405,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
         <v>575</v>
       </c>
@@ -15545,7 +15523,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
         <v>582</v>
       </c>
@@ -15663,7 +15641,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
         <v>586</v>
       </c>
@@ -15785,7 +15763,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
         <v>595</v>
       </c>
@@ -15907,7 +15885,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
         <v>602</v>
       </c>
@@ -16027,7 +16005,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
         <v>608</v>
       </c>
@@ -16145,7 +16123,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
         <v>612</v>
       </c>
@@ -16265,7 +16243,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
         <v>619</v>
       </c>
@@ -16385,7 +16363,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>625</v>
       </c>
@@ -16507,7 +16485,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="116" hidden="true">
+    <row r="116">
       <c r="A116" t="s" s="2">
         <v>632</v>
       </c>
@@ -16625,7 +16603,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
         <v>633</v>
       </c>
@@ -16745,7 +16723,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
         <v>634</v>
       </c>
@@ -16867,7 +16845,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="119" hidden="true">
+    <row r="119">
       <c r="A119" t="s" s="2">
         <v>635</v>
       </c>
@@ -16989,7 +16967,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
         <v>640</v>
       </c>
@@ -17107,7 +17085,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
         <v>641</v>
       </c>
@@ -17227,7 +17205,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
         <v>642</v>
       </c>
@@ -17347,7 +17325,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
         <v>643</v>
       </c>
@@ -17471,7 +17449,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
         <v>644</v>
       </c>
@@ -17589,7 +17567,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="125" hidden="true">
+    <row r="125">
       <c r="A125" t="s" s="2">
         <v>646</v>
       </c>
@@ -17709,7 +17687,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
         <v>648</v>
       </c>
@@ -17831,7 +17809,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
         <v>650</v>
       </c>
@@ -17951,7 +17929,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
         <v>652</v>
       </c>
@@ -18071,7 +18049,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="129" hidden="true">
+    <row r="129">
       <c r="A129" t="s" s="2">
         <v>654</v>
       </c>
@@ -18191,7 +18169,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
         <v>656</v>
       </c>
@@ -18313,7 +18291,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="131" hidden="true">
+    <row r="131">
       <c r="A131" t="s" s="2">
         <v>658</v>
       </c>
@@ -18437,7 +18415,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
         <v>659</v>
       </c>
@@ -18555,7 +18533,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="133" hidden="true">
+    <row r="133">
       <c r="A133" t="s" s="2">
         <v>660</v>
       </c>
@@ -18675,7 +18653,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="134" hidden="true">
+    <row r="134">
       <c r="A134" t="s" s="2">
         <v>661</v>
       </c>
@@ -18797,7 +18775,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="135" hidden="true">
+    <row r="135">
       <c r="A135" t="s" s="2">
         <v>662</v>
       </c>
@@ -18917,7 +18895,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="136" hidden="true">
+    <row r="136">
       <c r="A136" t="s" s="2">
         <v>663</v>
       </c>
@@ -19037,7 +19015,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
         <v>664</v>
       </c>
@@ -19157,7 +19135,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="138" hidden="true">
+    <row r="138">
       <c r="A138" t="s" s="2">
         <v>665</v>
       </c>
@@ -19279,7 +19257,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="139" hidden="true">
+    <row r="139">
       <c r="A139" t="s" s="2">
         <v>666</v>
       </c>
@@ -19403,7 +19381,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="140" hidden="true">
+    <row r="140">
       <c r="A140" t="s" s="2">
         <v>667</v>
       </c>
@@ -19521,7 +19499,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="141" hidden="true">
+    <row r="141">
       <c r="A141" t="s" s="2">
         <v>668</v>
       </c>
@@ -19641,7 +19619,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="142" hidden="true">
+    <row r="142">
       <c r="A142" t="s" s="2">
         <v>669</v>
       </c>
@@ -19763,7 +19741,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="143" hidden="true">
+    <row r="143">
       <c r="A143" t="s" s="2">
         <v>670</v>
       </c>
@@ -19883,7 +19861,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="144" hidden="true">
+    <row r="144">
       <c r="A144" t="s" s="2">
         <v>671</v>
       </c>
@@ -20003,7 +19981,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="145" hidden="true">
+    <row r="145">
       <c r="A145" t="s" s="2">
         <v>672</v>
       </c>
@@ -20123,7 +20101,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146" hidden="true">
+    <row r="146">
       <c r="A146" t="s" s="2">
         <v>673</v>
       </c>
@@ -20245,7 +20223,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="147" hidden="true">
+    <row r="147">
       <c r="A147" t="s" s="2">
         <v>674</v>
       </c>
@@ -20369,7 +20347,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="148" hidden="true">
+    <row r="148">
       <c r="A148" t="s" s="2">
         <v>675</v>
       </c>
@@ -20487,7 +20465,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="149" hidden="true">
+    <row r="149">
       <c r="A149" t="s" s="2">
         <v>676</v>
       </c>
@@ -20607,7 +20585,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="150" hidden="true">
+    <row r="150">
       <c r="A150" t="s" s="2">
         <v>677</v>
       </c>
@@ -20729,7 +20707,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="151" hidden="true">
+    <row r="151">
       <c r="A151" t="s" s="2">
         <v>678</v>
       </c>
@@ -20849,7 +20827,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="152" hidden="true">
+    <row r="152">
       <c r="A152" t="s" s="2">
         <v>679</v>
       </c>
@@ -20969,7 +20947,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="153" hidden="true">
+    <row r="153">
       <c r="A153" t="s" s="2">
         <v>680</v>
       </c>
@@ -21089,7 +21067,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="154" hidden="true">
+    <row r="154">
       <c r="A154" t="s" s="2">
         <v>681</v>
       </c>
@@ -21211,7 +21189,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="155" hidden="true">
+    <row r="155">
       <c r="A155" t="s" s="2">
         <v>682</v>
       </c>
@@ -21335,7 +21313,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
         <v>683</v>
       </c>
@@ -21453,7 +21431,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="157" hidden="true">
+    <row r="157">
       <c r="A157" t="s" s="2">
         <v>684</v>
       </c>
@@ -21573,7 +21551,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="158" hidden="true">
+    <row r="158">
       <c r="A158" t="s" s="2">
         <v>685</v>
       </c>
@@ -21695,7 +21673,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="159" hidden="true">
+    <row r="159">
       <c r="A159" t="s" s="2">
         <v>686</v>
       </c>
@@ -21815,7 +21793,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
         <v>687</v>
       </c>
@@ -21935,7 +21913,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="161" hidden="true">
+    <row r="161">
       <c r="A161" t="s" s="2">
         <v>688</v>
       </c>
@@ -22055,7 +22033,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="162" hidden="true">
+    <row r="162">
       <c r="A162" t="s" s="2">
         <v>689</v>
       </c>
@@ -22177,7 +22155,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="163" hidden="true">
+    <row r="163">
       <c r="A163" t="s" s="2">
         <v>690</v>
       </c>
@@ -22301,7 +22279,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="164" hidden="true">
+    <row r="164">
       <c r="A164" t="s" s="2">
         <v>692</v>
       </c>
@@ -22419,7 +22397,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
         <v>693</v>
       </c>
@@ -22539,7 +22517,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="166" hidden="true">
+    <row r="166">
       <c r="A166" t="s" s="2">
         <v>694</v>
       </c>
@@ -22661,7 +22639,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="167" hidden="true">
+    <row r="167">
       <c r="A167" t="s" s="2">
         <v>695</v>
       </c>
@@ -22781,7 +22759,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="168" hidden="true">
+    <row r="168">
       <c r="A168" t="s" s="2">
         <v>696</v>
       </c>
@@ -22901,7 +22879,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="169" hidden="true">
+    <row r="169">
       <c r="A169" t="s" s="2">
         <v>697</v>
       </c>
@@ -23021,7 +22999,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="170" hidden="true">
+    <row r="170">
       <c r="A170" t="s" s="2">
         <v>698</v>
       </c>
@@ -23143,7 +23121,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="171" hidden="true">
+    <row r="171">
       <c r="A171" t="s" s="2">
         <v>699</v>
       </c>
@@ -23265,7 +23243,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="172" hidden="true">
+    <row r="172">
       <c r="A172" t="s" s="2">
         <v>700</v>
       </c>
@@ -23385,7 +23363,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="173" hidden="true">
+    <row r="173">
       <c r="A173" t="s" s="2">
         <v>704</v>
       </c>
@@ -23509,7 +23487,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="174" hidden="true">
+    <row r="174">
       <c r="A174" t="s" s="2">
         <v>705</v>
       </c>
@@ -23627,7 +23605,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="175" hidden="true">
+    <row r="175">
       <c r="A175" t="s" s="2">
         <v>707</v>
       </c>
@@ -23747,7 +23725,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="176" hidden="true">
+    <row r="176">
       <c r="A176" t="s" s="2">
         <v>709</v>
       </c>
@@ -23869,7 +23847,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="177" hidden="true">
+    <row r="177">
       <c r="A177" t="s" s="2">
         <v>711</v>
       </c>
@@ -23991,7 +23969,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="178" hidden="true">
+    <row r="178">
       <c r="A178" t="s" s="2">
         <v>713</v>
       </c>
@@ -24111,7 +24089,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="179" hidden="true">
+    <row r="179">
       <c r="A179" t="s" s="2">
         <v>715</v>
       </c>
@@ -24231,7 +24209,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="180" hidden="true">
+    <row r="180">
       <c r="A180" t="s" s="2">
         <v>717</v>
       </c>
@@ -24353,7 +24331,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="181" hidden="true">
+    <row r="181">
       <c r="A181" t="s" s="2">
         <v>719</v>
       </c>
@@ -24451,7 +24429,7 @@
         <v>93</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>723</v>
+        <v>479</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>105</v>
@@ -24475,12 +24453,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="182" hidden="true">
+    <row r="182">
       <c r="A182" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24564,7 +24542,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24597,12 +24575,12 @@
         <v>492</v>
       </c>
     </row>
-    <row r="183" hidden="true">
+    <row r="183">
       <c r="A183" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24628,10 +24606,10 @@
         <v>83</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>563</v>
@@ -24686,7 +24664,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24720,24 +24698,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP183">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI182">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7056" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7056" uniqueCount="728">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T20:51:53+00:00</t>
+    <t>2024-06-25T21:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1099,7 +1099,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|Location|Device)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|http://hl7.dk/fhir/core/StructureDefinition/dk-core-location|Device)
 </t>
   </si>
   <si>
@@ -1244,7 +1244,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|Organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1656,6 +1656,9 @@
   </si>
   <si>
     <t>Observation.method.coding.system</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct|http://snomed.info/sct/554471000005108</t>
   </si>
   <si>
     <t>Observation.method.coding:SCTCode.version</t>
@@ -2574,7 +2577,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="218.88671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -14007,7 +14010,7 @@
         <v>82</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>294</v>
+        <v>532</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>82</v>
@@ -14081,10 +14084,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14201,10 +14204,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14321,10 +14324,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14441,10 +14444,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14563,10 +14566,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14685,10 +14688,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14711,16 +14714,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14770,7 +14773,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14788,27 +14791,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14831,16 +14834,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14890,7 +14893,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14908,27 +14911,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14951,19 +14954,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15012,7 +15015,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15024,7 +15027,7 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -15033,10 +15036,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15047,10 +15050,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15165,10 +15168,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15285,14 +15288,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15314,10 +15317,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>142</v>
@@ -15372,7 +15375,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15407,10 +15410,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15433,13 +15436,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15490,7 +15493,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15499,7 +15502,7 @@
         <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>105</v>
@@ -15511,10 +15514,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15525,10 +15528,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15551,13 +15554,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15608,7 +15611,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15617,7 +15620,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>105</v>
@@ -15629,10 +15632,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15643,10 +15646,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15672,16 +15675,16 @@
         <v>191</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15709,10 +15712,10 @@
         <v>117</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15730,7 +15733,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15748,10 +15751,10 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>491</v>
@@ -15765,10 +15768,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15794,16 +15797,16 @@
         <v>191</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15831,10 +15834,10 @@
         <v>206</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15852,7 +15855,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15870,10 +15873,10 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>491</v>
@@ -15887,10 +15890,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15913,17 +15916,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15972,7 +15975,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15996,7 +15999,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -16007,10 +16010,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16036,10 +16039,10 @@
         <v>216</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16090,7 +16093,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16111,10 +16114,10 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16125,10 +16128,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16151,16 +16154,16 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16210,7 +16213,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16231,10 +16234,10 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16245,10 +16248,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16271,16 +16274,16 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16330,7 +16333,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16351,10 +16354,10 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16365,10 +16368,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16391,19 +16394,19 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16452,7 +16455,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16473,10 +16476,10 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16487,10 +16490,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16605,10 +16608,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16725,14 +16728,14 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16754,10 +16757,10 @@
         <v>139</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>142</v>
@@ -16812,7 +16815,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16847,10 +16850,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16876,13 +16879,13 @@
         <v>191</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O119" t="s" s="2">
         <v>205</v>
@@ -16934,7 +16937,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>93</v>
@@ -16952,7 +16955,7 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>211</v>
@@ -16969,10 +16972,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17087,10 +17090,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17207,10 +17210,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17327,10 +17330,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>238</v>
@@ -17451,10 +17454,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17569,10 +17572,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17689,10 +17692,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17811,10 +17814,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17931,10 +17934,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18051,10 +18054,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18171,10 +18174,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18293,10 +18296,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>289</v>
@@ -18417,10 +18420,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18535,10 +18538,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18655,10 +18658,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18777,10 +18780,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18897,10 +18900,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19017,10 +19020,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19137,10 +19140,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19259,10 +19262,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>300</v>
@@ -19383,10 +19386,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19501,10 +19504,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19621,10 +19624,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19743,10 +19746,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19863,10 +19866,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19983,10 +19986,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20103,10 +20106,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20225,10 +20228,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>311</v>
@@ -20349,10 +20352,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20467,10 +20470,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20587,10 +20590,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20709,10 +20712,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20829,10 +20832,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20949,10 +20952,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21069,10 +21072,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21191,10 +21194,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>322</v>
@@ -21315,10 +21318,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21433,10 +21436,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21553,10 +21556,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21675,10 +21678,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21795,10 +21798,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21915,10 +21918,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22035,10 +22038,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22157,10 +22160,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>333</v>
@@ -22188,7 +22191,7 @@
         <v>228</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M163" t="s" s="2">
         <v>230</v>
@@ -22281,10 +22284,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22399,10 +22402,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22519,10 +22522,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22641,10 +22644,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22761,10 +22764,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22881,10 +22884,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23001,10 +23004,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23123,10 +23126,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23245,10 +23248,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23274,13 +23277,13 @@
         <v>407</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>409</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O172" t="s" s="2">
         <v>411</v>
@@ -23330,7 +23333,7 @@
         <v>225</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23348,7 +23351,7 @@
         <v>82</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>415</v>
@@ -23365,10 +23368,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>419</v>
@@ -23396,13 +23399,13 @@
         <v>420</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>409</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>411</v>
@@ -23454,7 +23457,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23472,7 +23475,7 @@
         <v>82</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>415</v>
@@ -23489,10 +23492,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23607,10 +23610,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23727,10 +23730,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23849,10 +23852,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23971,10 +23974,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24091,10 +24094,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24211,10 +24214,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24333,10 +24336,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24362,13 +24365,13 @@
         <v>191</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O181" t="s" s="2">
         <v>475</v>
@@ -24420,7 +24423,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24455,10 +24458,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24542,7 +24545,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24577,10 +24580,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24606,16 +24609,16 @@
         <v>83</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24664,7 +24667,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24685,10 +24688,10 @@
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Danish Core Observation Profiles</t>
+    <t>Danish Core Observation Profile</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1929,7 +1929,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7056" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7056" uniqueCount="727">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Danish Core Observation Profile</t>
+    <t>Danish Core Observation Profiles</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:12:58+00:00</t>
+    <t>2024-10-17T12:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1099,7 +1099,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|http://hl7.dk/fhir/core/StructureDefinition/dk-core-location|Device)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|Location|Device)
 </t>
   </si>
   <si>
@@ -1244,7 +1244,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1656,9 +1656,6 @@
   </si>
   <si>
     <t>Observation.method.coding.system</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct|http://snomed.info/sct/554471000005108</t>
   </si>
   <si>
     <t>Observation.method.coding:SCTCode.version</t>
@@ -14010,7 +14007,7 @@
         <v>82</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>532</v>
+        <v>294</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>82</v>
@@ -14084,10 +14081,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14204,10 +14201,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14324,10 +14321,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14444,10 +14441,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14566,10 +14563,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14688,10 +14685,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14714,16 +14711,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14773,7 +14770,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14791,27 +14788,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="AM101" t="s" s="2">
+      <c r="AN101" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="AN101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>550</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14834,16 +14831,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14893,7 +14890,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14911,27 +14908,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AM102" t="s" s="2">
+      <c r="AN102" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="AN102" t="s" s="2">
+      <c r="AO102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP102" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>559</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14954,19 +14951,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15015,7 +15012,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15027,19 +15024,19 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="AK103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM103" t="s" s="2">
+      <c r="AN103" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15050,10 +15047,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15168,10 +15165,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15288,14 +15285,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15317,10 +15314,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>142</v>
@@ -15375,7 +15372,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15410,10 +15407,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15436,13 +15433,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15493,7 +15490,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15502,7 +15499,7 @@
         <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>105</v>
@@ -15514,10 +15511,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15528,10 +15525,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15554,13 +15551,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15611,7 +15608,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15620,7 +15617,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>105</v>
@@ -15632,10 +15629,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15646,10 +15643,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15675,16 +15672,16 @@
         <v>191</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="N109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15712,11 +15709,11 @@
         <v>117</v>
       </c>
       <c r="Y109" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="Z109" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="Z109" t="s" s="2">
-        <v>593</v>
-      </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15733,7 +15730,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15751,10 +15748,10 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>491</v>
@@ -15768,10 +15765,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15797,16 +15794,16 @@
         <v>191</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15834,11 +15831,11 @@
         <v>206</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="Z110" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="Z110" t="s" s="2">
-        <v>602</v>
-      </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15855,7 +15852,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15873,10 +15870,10 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AM110" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>491</v>
@@ -15890,10 +15887,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15916,17 +15913,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15975,7 +15972,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15999,7 +15996,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -16010,10 +16007,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16039,10 +16036,10 @@
         <v>216</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16093,7 +16090,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16114,10 +16111,10 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16128,10 +16125,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16154,16 +16151,16 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16213,7 +16210,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16234,10 +16231,10 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AN113" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16248,10 +16245,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16274,16 +16271,16 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16333,7 +16330,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16354,10 +16351,10 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16368,10 +16365,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16394,19 +16391,19 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16455,7 +16452,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16476,10 +16473,10 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16490,10 +16487,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16608,10 +16605,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16728,14 +16725,14 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16757,10 +16754,10 @@
         <v>139</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>142</v>
@@ -16815,7 +16812,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16850,10 +16847,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16879,13 +16876,13 @@
         <v>191</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="O119" t="s" s="2">
         <v>205</v>
@@ -16937,7 +16934,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>93</v>
@@ -16955,7 +16952,7 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>211</v>
@@ -16972,10 +16969,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17090,10 +17087,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17210,10 +17207,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17330,10 +17327,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>238</v>
@@ -17454,10 +17451,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17572,10 +17569,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B125" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17692,10 +17689,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B126" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17814,10 +17811,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="B127" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17934,10 +17931,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>654</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18054,10 +18051,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B129" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18174,10 +18171,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="B130" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18296,10 +18293,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>289</v>
@@ -18420,10 +18417,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18538,10 +18535,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18658,10 +18655,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18780,10 +18777,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18900,10 +18897,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19020,10 +19017,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19140,10 +19137,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19262,10 +19259,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>300</v>
@@ -19386,10 +19383,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19504,10 +19501,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19624,10 +19621,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19746,10 +19743,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19866,10 +19863,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19986,10 +19983,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20106,10 +20103,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20228,10 +20225,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>311</v>
@@ -20352,10 +20349,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20470,10 +20467,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20590,10 +20587,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20712,10 +20709,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20832,10 +20829,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20952,10 +20949,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21072,10 +21069,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21194,10 +21191,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>322</v>
@@ -21318,10 +21315,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21436,10 +21433,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21556,10 +21553,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21678,10 +21675,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21798,10 +21795,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21918,10 +21915,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22038,10 +22035,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22160,10 +22157,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>333</v>
@@ -22191,7 +22188,7 @@
         <v>228</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="M163" t="s" s="2">
         <v>230</v>
@@ -22284,10 +22281,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22402,10 +22399,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22522,10 +22519,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22644,10 +22641,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22764,10 +22761,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22884,10 +22881,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23004,10 +23001,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23126,10 +23123,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23248,10 +23245,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23277,13 +23274,13 @@
         <v>407</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>409</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="O172" t="s" s="2">
         <v>411</v>
@@ -23333,7 +23330,7 @@
         <v>225</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23351,7 +23348,7 @@
         <v>82</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>415</v>
@@ -23368,10 +23365,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>419</v>
@@ -23399,13 +23396,13 @@
         <v>420</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>409</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>411</v>
@@ -23457,7 +23454,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23475,7 +23472,7 @@
         <v>82</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>415</v>
@@ -23492,10 +23489,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="B174" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23610,10 +23607,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="B175" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23730,10 +23727,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="B176" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23852,10 +23849,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="B177" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23974,10 +23971,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="B178" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24094,10 +24091,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="B179" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24214,10 +24211,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="B180" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24336,10 +24333,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24365,13 +24362,13 @@
         <v>191</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="M181" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="M181" t="s" s="2">
+      <c r="N181" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="O181" t="s" s="2">
         <v>475</v>
@@ -24423,7 +24420,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24458,10 +24455,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24545,7 +24542,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24580,10 +24577,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24609,16 +24606,16 @@
         <v>83</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="M183" t="s" s="2">
-        <v>727</v>
-      </c>
       <c r="N183" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="O183" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24667,7 +24664,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24688,10 +24685,10 @@
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AN183" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AN183" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7056" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7056" uniqueCount="728">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Danish Core Observation Profiles</t>
+    <t>Danish Core Observation Profile</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:15:17+00:00</t>
+    <t>2024-10-18T06:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1099,7 +1099,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|Location|Device)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|http://hl7.dk/fhir/core/StructureDefinition/dk-core-location|Device)
 </t>
   </si>
   <si>
@@ -1244,7 +1244,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1656,6 +1656,9 @@
   </si>
   <si>
     <t>Observation.method.coding.system</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct|http://snomed.info/sct/554471000005108</t>
   </si>
   <si>
     <t>Observation.method.coding:SCTCode.version</t>
@@ -14007,7 +14010,7 @@
         <v>82</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>294</v>
+        <v>532</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>82</v>
@@ -14081,10 +14084,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14201,10 +14204,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14321,10 +14324,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14441,10 +14444,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14563,10 +14566,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14685,10 +14688,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14711,16 +14714,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14770,7 +14773,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14788,27 +14791,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14831,16 +14834,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14890,7 +14893,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14908,27 +14911,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14951,19 +14954,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15012,7 +15015,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15024,7 +15027,7 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -15033,10 +15036,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15047,10 +15050,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15165,10 +15168,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15285,14 +15288,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15314,10 +15317,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>142</v>
@@ -15372,7 +15375,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15407,10 +15410,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15433,13 +15436,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15490,7 +15493,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15499,7 +15502,7 @@
         <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>105</v>
@@ -15511,10 +15514,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15525,10 +15528,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15551,13 +15554,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15608,7 +15611,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15617,7 +15620,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>105</v>
@@ -15629,10 +15632,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15643,10 +15646,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15672,16 +15675,16 @@
         <v>191</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15709,10 +15712,10 @@
         <v>117</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15730,7 +15733,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15748,10 +15751,10 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>491</v>
@@ -15765,10 +15768,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15794,16 +15797,16 @@
         <v>191</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15831,10 +15834,10 @@
         <v>206</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15852,7 +15855,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15870,10 +15873,10 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>491</v>
@@ -15887,10 +15890,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15913,17 +15916,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15972,7 +15975,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15996,7 +15999,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -16007,10 +16010,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16036,10 +16039,10 @@
         <v>216</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16090,7 +16093,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16111,10 +16114,10 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16125,10 +16128,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16151,16 +16154,16 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16210,7 +16213,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16231,10 +16234,10 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16245,10 +16248,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16271,16 +16274,16 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16330,7 +16333,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16351,10 +16354,10 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16365,10 +16368,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16391,19 +16394,19 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16452,7 +16455,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16473,10 +16476,10 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16487,10 +16490,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16605,10 +16608,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16725,14 +16728,14 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16754,10 +16757,10 @@
         <v>139</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>142</v>
@@ -16812,7 +16815,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16847,10 +16850,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16876,13 +16879,13 @@
         <v>191</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O119" t="s" s="2">
         <v>205</v>
@@ -16934,7 +16937,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>93</v>
@@ -16952,7 +16955,7 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>211</v>
@@ -16969,10 +16972,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17087,10 +17090,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17207,10 +17210,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17327,10 +17330,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>238</v>
@@ -17451,10 +17454,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17569,10 +17572,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17689,10 +17692,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17811,10 +17814,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17931,10 +17934,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18051,10 +18054,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18171,10 +18174,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18293,10 +18296,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>289</v>
@@ -18417,10 +18420,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18535,10 +18538,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18655,10 +18658,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18777,10 +18780,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18897,10 +18900,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19017,10 +19020,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19137,10 +19140,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19259,10 +19262,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>300</v>
@@ -19383,10 +19386,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19501,10 +19504,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19621,10 +19624,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19743,10 +19746,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19863,10 +19866,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19983,10 +19986,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20103,10 +20106,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20225,10 +20228,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>311</v>
@@ -20349,10 +20352,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20467,10 +20470,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20587,10 +20590,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20709,10 +20712,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20829,10 +20832,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20949,10 +20952,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21069,10 +21072,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21191,10 +21194,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>322</v>
@@ -21315,10 +21318,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21433,10 +21436,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21553,10 +21556,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21675,10 +21678,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21795,10 +21798,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21915,10 +21918,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22035,10 +22038,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22157,10 +22160,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>333</v>
@@ -22188,7 +22191,7 @@
         <v>228</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M163" t="s" s="2">
         <v>230</v>
@@ -22281,10 +22284,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22399,10 +22402,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22519,10 +22522,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22641,10 +22644,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22761,10 +22764,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22881,10 +22884,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23001,10 +23004,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23123,10 +23126,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23245,10 +23248,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23274,13 +23277,13 @@
         <v>407</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>409</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O172" t="s" s="2">
         <v>411</v>
@@ -23330,7 +23333,7 @@
         <v>225</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23348,7 +23351,7 @@
         <v>82</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>415</v>
@@ -23365,10 +23368,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>419</v>
@@ -23396,13 +23399,13 @@
         <v>420</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>409</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>411</v>
@@ -23454,7 +23457,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23472,7 +23475,7 @@
         <v>82</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>415</v>
@@ -23489,10 +23492,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23607,10 +23610,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23727,10 +23730,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23849,10 +23852,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23971,10 +23974,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24091,10 +24094,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24211,10 +24214,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24333,10 +24336,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24362,13 +24365,13 @@
         <v>191</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O181" t="s" s="2">
         <v>475</v>
@@ -24420,7 +24423,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24455,10 +24458,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24542,7 +24545,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24577,10 +24580,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24606,16 +24609,16 @@
         <v>83</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24664,7 +24667,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24685,10 +24688,10 @@
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7056" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7056" uniqueCount="727">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.4.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Danish Core Observation Profile</t>
+    <t>Danish Core Observation Profiles</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T12:45:46+00:00</t>
+    <t>2024-11-15T12:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1099,7 +1099,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|http://hl7.dk/fhir/core/StructureDefinition/dk-core-location|Device)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|Group|Location|Device)
 </t>
   </si>
   <si>
@@ -1244,7 +1244,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1656,9 +1656,6 @@
   </si>
   <si>
     <t>Observation.method.coding.system</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct|http://snomed.info/sct/554471000005108</t>
   </si>
   <si>
     <t>Observation.method.coding:SCTCode.version</t>
@@ -14010,7 +14007,7 @@
         <v>82</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>532</v>
+        <v>294</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>82</v>
@@ -14084,10 +14081,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14204,10 +14201,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14324,10 +14321,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14444,10 +14441,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14566,10 +14563,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14688,10 +14685,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14714,16 +14711,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14773,7 +14770,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14791,27 +14788,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="AM101" t="s" s="2">
+      <c r="AN101" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="AN101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>550</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14834,16 +14831,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14893,7 +14890,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14911,27 +14908,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AM102" t="s" s="2">
+      <c r="AN102" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="AN102" t="s" s="2">
+      <c r="AO102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP102" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>559</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14954,19 +14951,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15015,7 +15012,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15027,19 +15024,19 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="AK103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM103" t="s" s="2">
+      <c r="AN103" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15050,10 +15047,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15168,10 +15165,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15288,14 +15285,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15317,10 +15314,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>142</v>
@@ -15375,7 +15372,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15410,10 +15407,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15436,13 +15433,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15493,7 +15490,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15502,7 +15499,7 @@
         <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>105</v>
@@ -15514,10 +15511,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15528,10 +15525,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15554,13 +15551,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15611,7 +15608,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15620,7 +15617,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>105</v>
@@ -15632,10 +15629,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15646,10 +15643,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15675,16 +15672,16 @@
         <v>191</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="N109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15712,11 +15709,11 @@
         <v>117</v>
       </c>
       <c r="Y109" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="Z109" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="Z109" t="s" s="2">
-        <v>593</v>
-      </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15733,7 +15730,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15751,10 +15748,10 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>491</v>
@@ -15768,10 +15765,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15797,16 +15794,16 @@
         <v>191</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15834,11 +15831,11 @@
         <v>206</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="Z110" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="Z110" t="s" s="2">
-        <v>602</v>
-      </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15855,7 +15852,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15873,10 +15870,10 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AM110" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>491</v>
@@ -15890,10 +15887,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15916,17 +15913,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15975,7 +15972,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15999,7 +15996,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -16010,10 +16007,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16039,10 +16036,10 @@
         <v>216</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16093,7 +16090,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16114,10 +16111,10 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16128,10 +16125,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16154,16 +16151,16 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16213,7 +16210,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16234,10 +16231,10 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AN113" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16248,10 +16245,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16274,16 +16271,16 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16333,7 +16330,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16354,10 +16351,10 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16368,10 +16365,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16394,19 +16391,19 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16455,7 +16452,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16476,10 +16473,10 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16490,10 +16487,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16608,10 +16605,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16728,14 +16725,14 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16757,10 +16754,10 @@
         <v>139</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>142</v>
@@ -16815,7 +16812,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16850,10 +16847,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16879,13 +16876,13 @@
         <v>191</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="O119" t="s" s="2">
         <v>205</v>
@@ -16937,7 +16934,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>93</v>
@@ -16955,7 +16952,7 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>211</v>
@@ -16972,10 +16969,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17090,10 +17087,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17210,10 +17207,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17330,10 +17327,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>238</v>
@@ -17454,10 +17451,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17572,10 +17569,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B125" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17692,10 +17689,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B126" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17814,10 +17811,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="B127" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17934,10 +17931,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>654</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18054,10 +18051,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B129" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18174,10 +18171,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="B130" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18296,10 +18293,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>289</v>
@@ -18420,10 +18417,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18538,10 +18535,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18658,10 +18655,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18780,10 +18777,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18900,10 +18897,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19020,10 +19017,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19140,10 +19137,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19262,10 +19259,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>300</v>
@@ -19386,10 +19383,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19504,10 +19501,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19624,10 +19621,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19746,10 +19743,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19866,10 +19863,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19986,10 +19983,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20106,10 +20103,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20228,10 +20225,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>311</v>
@@ -20352,10 +20349,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20470,10 +20467,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20590,10 +20587,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20712,10 +20709,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20832,10 +20829,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20952,10 +20949,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21072,10 +21069,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21194,10 +21191,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>322</v>
@@ -21318,10 +21315,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21436,10 +21433,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21556,10 +21553,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21678,10 +21675,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21798,10 +21795,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21918,10 +21915,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22038,10 +22035,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22160,10 +22157,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>333</v>
@@ -22191,7 +22188,7 @@
         <v>228</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="M163" t="s" s="2">
         <v>230</v>
@@ -22284,10 +22281,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22402,10 +22399,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22522,10 +22519,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22644,10 +22641,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22764,10 +22761,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22884,10 +22881,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23004,10 +23001,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23126,10 +23123,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23248,10 +23245,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23277,13 +23274,13 @@
         <v>407</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>409</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="O172" t="s" s="2">
         <v>411</v>
@@ -23333,7 +23330,7 @@
         <v>225</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23351,7 +23348,7 @@
         <v>82</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>415</v>
@@ -23368,10 +23365,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>419</v>
@@ -23399,13 +23396,13 @@
         <v>420</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>409</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>411</v>
@@ -23457,7 +23454,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23475,7 +23472,7 @@
         <v>82</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>415</v>
@@ -23492,10 +23489,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="B174" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23610,10 +23607,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="B175" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23730,10 +23727,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="B176" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23852,10 +23849,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="B177" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23974,10 +23971,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="B178" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24094,10 +24091,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="B179" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24214,10 +24211,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="B180" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24336,10 +24333,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24365,13 +24362,13 @@
         <v>191</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="M181" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="M181" t="s" s="2">
+      <c r="N181" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="O181" t="s" s="2">
         <v>475</v>
@@ -24423,7 +24420,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24458,10 +24455,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24545,7 +24542,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24580,10 +24577,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24609,16 +24606,16 @@
         <v>83</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="M183" t="s" s="2">
-        <v>727</v>
-      </c>
       <c r="N183" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="O183" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24667,7 +24664,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24688,10 +24685,10 @@
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AN183" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AN183" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:38:49+00:00</t>
+    <t>2024-12-11T09:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T09:50:58+00:00</t>
+    <t>2024-12-16T15:09:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-observation.xlsx
+++ b/StructureDefinition-dk-core-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
